--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1316-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1316-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F549F29-D3B9-425C-A440-CE9AF7D23035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B79C03-AFBE-4A7A-BC5F-51F99B09763C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6FD17C19-5A62-431A-82C6-A30A89006856}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D6BC359B-3420-4352-83E5-D5351CCCE1BC}"/>
   </bookViews>
   <sheets>
     <sheet name="1316-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,23 +1472,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C23B563-13DE-43F5-853B-64AA566596C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769C935C-8027-467E-8C7C-B5154D717FFA}">
   <dimension ref="A1:R60"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1642,7 +1642,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2022</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2021</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2020</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2019</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2018</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2017</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2016</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2015</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2014</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2013</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2012</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2011</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2010</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2009</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2008</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2007</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2006</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2005</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2004</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2003</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2002</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2001</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>2000</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>1999</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>1998</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>1997</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>1996</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>1995</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
         <v>1994</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>1993</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
         <v>1992</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>1991</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="37">
         <v>1990</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <v>1989</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="37" t="s">
         <v>43</v>
       </c>
